--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-09-24 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -705,13 +705,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-0.02</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="9">
@@ -751,13 +751,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.7</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="11">
@@ -774,13 +774,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.69</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="12">
@@ -1050,13 +1050,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>-0.02</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="24">
@@ -1073,10 +1073,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0.18</v>
@@ -1096,13 +1096,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-0.07</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="26">
@@ -1119,13 +1119,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-0.13</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="27">
@@ -1395,13 +1395,13 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="39">
@@ -1418,13 +1418,13 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.17</v>
+        <v>0.07</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="40">
@@ -1441,13 +1441,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -1464,13 +1464,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="42">
@@ -1513,10 +1513,10 @@
         <v>-0.39</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="44">
@@ -1536,10 +1536,10 @@
         <v>-0.29</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="45">
@@ -1562,7 +1562,7 @@
         <v>0.2</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="46">
@@ -1740,13 +1740,13 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0.23</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="54">
@@ -1763,13 +1763,13 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="55">
@@ -1786,13 +1786,13 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="56">
@@ -1809,13 +1809,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="57">
@@ -1881,10 +1881,10 @@
         <v>-0.14</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="60">
@@ -2085,13 +2085,13 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="69">
@@ -2108,13 +2108,13 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>-0.23</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="70">
@@ -2131,13 +2131,13 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>0.14</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="71">
@@ -2154,13 +2154,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="72">
@@ -2430,13 +2430,13 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="84">
@@ -2453,13 +2453,13 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="F84" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>-0.12</v>
       </c>
     </row>
     <row r="85">
@@ -2476,13 +2476,13 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="86">
@@ -2499,13 +2499,13 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="G86" s="2" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="87">
@@ -2778,10 +2778,10 @@
         <v>-0.44</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="99">
@@ -2798,13 +2798,13 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.69</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="100">
@@ -2844,13 +2844,13 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="102">
@@ -2893,10 +2893,10 @@
         <v>-0.63</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="104">
@@ -2916,10 +2916,10 @@
         <v>-0.6</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="105">
@@ -3120,13 +3120,13 @@
         <v>18</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="114">
@@ -3146,10 +3146,10 @@
         <v>-0.54</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="115">
@@ -3166,13 +3166,13 @@
         <v>18</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>-0.12</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="116">
@@ -3189,13 +3189,13 @@
         <v>18</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="117">
@@ -3241,7 +3241,7 @@
         <v>-0.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="119">
@@ -3264,7 +3264,7 @@
         <v>0.18</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="120">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:02</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_coquimbo.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
